--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120539122</v>
+        <v>120539074</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>91370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567281</v>
+        <v>567440</v>
       </c>
       <c r="R2" t="n">
-        <v>6432041</v>
+        <v>6432047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre. Dropptaggsvamp?</t>
+          <t>Gammal. Dropptaggsvamp?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120539054</v>
+        <v>120538655</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567441</v>
+        <v>567555</v>
       </c>
       <c r="R3" t="n">
-        <v>6432047</v>
+        <v>6432081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120538655</v>
+        <v>120538817</v>
       </c>
       <c r="B4" t="n">
         <v>105032</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567555</v>
+        <v>567551</v>
       </c>
       <c r="R4" t="n">
-        <v>6432081</v>
+        <v>6432070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120539074</v>
+        <v>120539054</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>91879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2014</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567440</v>
+        <v>567441</v>
       </c>
       <c r="R5" t="n">
         <v>6432047</v>
@@ -1103,11 +1103,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal. Dropptaggsvamp?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120538817</v>
+        <v>120539122</v>
       </c>
       <c r="B6" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,33 +1142,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567551</v>
+        <v>567281</v>
       </c>
       <c r="R6" t="n">
-        <v>6432070</v>
+        <v>6432041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,6 +1216,11 @@
           <t>2024-10-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre. Dropptaggsvamp?</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1243,6 +1243,348 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120583084</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567378</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6432176</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120582840</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567407</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6432152</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120582357</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57471</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567540</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6432054</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,6 +1581,771 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128834646</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128834689</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128834641</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128834611</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567423</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6432072</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128834565</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92780</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567454</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6432065</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128834527</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92126</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567515</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6432058</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128834675</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56898</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sj ngn strof+ ngt lock</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,6 +2346,854 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128886904</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567519</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6432080</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128885467</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567482</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6432063</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128886816</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92789</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567496</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6432063</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128886767</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567570</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6432065</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128885716</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567444</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6432050</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128885337</v>
+      </c>
+      <c r="B22" t="n">
+        <v>86987</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567537</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6432065</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128885509</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90881</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567470</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6432053</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128886952</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567312</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6432061</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92785</v>
+        <v>92790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128886816</v>
       </c>
       <c r="B19" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90881</v>
+        <v>90886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,6 +3193,1284 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128893549</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6432035</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128901291</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92806</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567482</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6432063</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128893756</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567289</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6432071</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128893894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>567377</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6432177</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128834653</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91911</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6432109</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Granlågan med ullticka</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128894108</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>567418</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6432134</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128893759</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>567485</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6432071</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128896818</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86809</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>427</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Puderspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>567519</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6432055</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist, Stefan Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128902008</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 39295, Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>567412</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6432068</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128893564</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vårum-Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>567533</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6432053</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128896704</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86851</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>445</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>567470</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6432053</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128901081</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87025</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vårum, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>567509</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6432056</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3406,32 +3406,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>92794</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3441,10 +3441,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3452,10 +3453,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R27" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,32 +3516,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>92794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3550,11 +3551,10 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R28" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3406,32 +3406,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>92794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3441,11 +3441,10 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3453,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R27" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3516,32 +3515,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B28" t="n">
-        <v>92794</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3551,10 +3550,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R28" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3734,45 +3734,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>92786</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3780,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R30" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3843,46 +3844,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>92786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R31" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>128834689</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>92834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R12" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,11 +1879,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1906,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>92830</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R13" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,6 +1988,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128886904</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Jan Aronsson, Gunilla Nilsson, Larsgunnar Nilsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
         <v>128886767</v>
       </c>
       <c r="B20" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128893549</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>128901291</v>
       </c>
       <c r="B26" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
         <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
         <v>128893894</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>128834653</v>
       </c>
       <c r="B29" t="n">
-        <v>91911</v>
+        <v>91915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,46 +3734,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>92790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3781,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R30" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3844,45 +3843,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B31" t="n">
-        <v>92786</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R31" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3956,7 +3956,7 @@
         <v>128896818</v>
       </c>
       <c r="B32" t="n">
-        <v>86809</v>
+        <v>86813</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92498</v>
+        <v>92502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
         <v>128893564</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128896704</v>
       </c>
       <c r="B35" t="n">
-        <v>86851</v>
+        <v>86855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>128901081</v>
       </c>
       <c r="B36" t="n">
-        <v>87025</v>
+        <v>87029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2660,7 +2660,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Gunilla Nilsson, Larsgunnar Nilsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3399,39 +3399,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Jan Aronsson, Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>92798</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3441,10 +3441,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3452,10 +3453,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R27" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,32 +3516,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>92798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3550,11 +3551,10 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R28" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>128834689</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128886904</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
         <v>128886767</v>
       </c>
       <c r="B20" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90890</v>
+        <v>90895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128893549</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>128901291</v>
       </c>
       <c r="B26" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,32 +3406,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>92803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3441,11 +3441,10 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3453,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R27" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3516,32 +3515,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B28" t="n">
-        <v>92798</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3551,10 +3550,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R28" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3628,7 +3628,7 @@
         <v>128834653</v>
       </c>
       <c r="B29" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,45 +3734,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>92790</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3780,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R30" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3843,46 +3844,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>92795</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R31" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3956,7 +3956,7 @@
         <v>128896818</v>
       </c>
       <c r="B32" t="n">
-        <v>86813</v>
+        <v>86818</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,59 +4062,51 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B33" t="n">
-        <v>92502</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R33" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4130,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,63 +4151,71 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>92507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R34" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,12 +4260,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
         <v>128896704</v>
       </c>
       <c r="B35" t="n">
-        <v>86855</v>
+        <v>86860</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>128901081</v>
       </c>
       <c r="B36" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3196,48 +3196,56 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128893549</v>
+        <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>92823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567445</v>
+        <v>567482</v>
       </c>
       <c r="R25" t="n">
-        <v>6432035</v>
+        <v>6432063</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3285,68 +3293,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128901291</v>
+        <v>128893894</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567482</v>
+        <v>567377</v>
       </c>
       <c r="R26" t="n">
-        <v>6432063</v>
+        <v>6432177</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3394,44 +3403,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3441,11 +3450,10 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3453,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R27" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3516,37 +3524,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128893756</v>
+        <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>92811</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3558,17 +3561,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567289</v>
+        <v>567385</v>
       </c>
       <c r="R28" t="n">
-        <v>6432071</v>
+        <v>6432109</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3592,12 +3595,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Granlågan med ullticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3613,22 +3621,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128834653</v>
+        <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>92803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3636,21 +3644,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3662,17 +3675,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567385</v>
+        <v>567418</v>
       </c>
       <c r="R29" t="n">
-        <v>6432109</v>
+        <v>6432134</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3696,17 +3709,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Granlågan med ullticka</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,12 +3730,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3844,10 +3852,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128894108</v>
+        <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>92803</v>
+        <v>86825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,26 +3863,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>427</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3886,17 +3894,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567418</v>
+        <v>567519</v>
       </c>
       <c r="R31" t="n">
-        <v>6432134</v>
+        <v>6432055</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,22 +3949,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist, Stefan Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128896818</v>
+        <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>86825</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,48 +3972,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>427</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567519</v>
+        <v>567533</v>
       </c>
       <c r="R32" t="n">
-        <v>6432055</v>
+        <v>6432053</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,63 +4050,71 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist, Stefan Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson, Jan Aronsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>92515</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R33" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4130,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4151,71 +4159,63 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128902008</v>
+        <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>92515</v>
+        <v>86867</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5836</v>
+        <v>445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567412</v>
+        <v>567470</v>
       </c>
       <c r="R34" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,48 +4260,48 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128896704</v>
+        <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>86867</v>
+        <v>87041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>445</v>
+        <v>3624</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567470</v>
+        <v>567509</v>
       </c>
       <c r="R35" t="n">
-        <v>6432053</v>
+        <v>6432056</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4366,38 +4366,46 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128901081</v>
+        <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>87041</v>
+        <v>92849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3624</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -4407,14 +4415,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567509</v>
+        <v>567440</v>
       </c>
       <c r="R36" t="n">
-        <v>6432056</v>
+        <v>6432029</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4441,12 +4449,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,12 +4470,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Susanne Hernqvist, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>92852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R12" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,11 +1879,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1906,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>92847</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R13" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,6 +1988,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>92816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,11 +3340,10 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3352,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R26" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3415,32 +3414,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>92811</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3450,10 +3449,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R27" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91931</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87041</v>
+        <v>87044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92812</v>
+        <v>92815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,45 +3633,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3679,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R29" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3742,46 +3743,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>92811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R30" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86828</v>
+        <v>86831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92520</v>
+        <v>92523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86870</v>
+        <v>86873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87044</v>
+        <v>87047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>92855</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R12" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,6 +1879,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,37 +1911,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>92855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R13" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,11 +1993,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3961,51 +3961,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>92523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R32" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4029,12 +4037,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,71 +4058,63 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B33" t="n">
-        <v>92523</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R33" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3633,46 +3633,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>92811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3680,10 +3679,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R29" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3743,45 +3742,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>92811</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R30" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3633,45 +3633,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3679,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R29" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3742,46 +3743,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>92811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R30" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>128834689</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128886904</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>128886767</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91934</v>
+        <v>91941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3633,46 +3633,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128893759</v>
+        <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>92818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3680,10 +3679,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567485</v>
+        <v>567418</v>
       </c>
       <c r="R29" t="n">
-        <v>6432071</v>
+        <v>6432134</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3743,45 +3742,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128894108</v>
+        <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>92811</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567418</v>
+        <v>567485</v>
       </c>
       <c r="R30" t="n">
-        <v>6432134</v>
+        <v>6432071</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86831</v>
+        <v>86835</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,59 +3961,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>92523</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R32" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4037,12 +4029,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,63 +4050,71 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>92530</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R33" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86873</v>
+        <v>86877</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87047</v>
+        <v>87051</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>92862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R12" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,11 +1879,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1906,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>92862</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R13" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,6 +1988,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3961,51 +3961,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>92530</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R32" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4029,12 +4037,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,71 +4058,63 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B33" t="n">
-        <v>92530</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R33" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87014</v>
+        <v>87021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91941</v>
+        <v>91948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86835</v>
+        <v>86842</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,59 +3961,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>92530</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R32" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4037,12 +4029,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,63 +4050,71 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>92537</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R33" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>128834689</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R12" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,6 +1879,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,37 +1911,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R13" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,11 +1993,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128886904</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>128886767</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B26" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,10 +3340,11 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3351,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R26" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3414,32 +3415,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3449,11 +3450,10 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R27" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91948</v>
+        <v>91950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86842</v>
+        <v>86844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92537</v>
+        <v>92539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>128834641</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128834611</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,11 +3340,10 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3352,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R26" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3415,32 +3414,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>92835</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3450,10 +3449,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R27" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91950</v>
+        <v>91958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86844</v>
+        <v>86845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92539</v>
+        <v>92553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87060</v>
+        <v>87061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -1586,7 +1586,7 @@
         <v>128834646</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,37 +1797,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128834641</v>
+        <v>128834611</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>92858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567385</v>
+        <v>567423</v>
       </c>
       <c r="R12" t="n">
-        <v>6432109</v>
+        <v>6432072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,11 +1879,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1906,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128834611</v>
+        <v>128834641</v>
       </c>
       <c r="B13" t="n">
-        <v>92857</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567423</v>
+        <v>567385</v>
       </c>
       <c r="R13" t="n">
-        <v>6432072</v>
+        <v>6432109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,6 +1988,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mkt utbredd på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,7 +2023,7 @@
         <v>128834565</v>
       </c>
       <c r="B14" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>128834527</v>
       </c>
       <c r="B15" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92553</v>
+        <v>92554</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2457,55 +2457,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128886816</v>
+        <v>128885467</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567496</v>
+        <v>567482</v>
       </c>
       <c r="R18" t="n">
         <v>6432063</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,67 +2550,67 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128885467</v>
+        <v>128886816</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vårum, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567482</v>
+        <v>567496</v>
       </c>
       <c r="R19" t="n">
         <v>6432063</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,12 +2655,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson, Susanne Hernqvist, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Larsgunnar Nilsson, Gunilla Nilsson, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3305,32 +3305,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B26" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,10 +3340,11 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3351,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R26" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3414,32 +3415,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>92822</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3449,11 +3450,10 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R27" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,51 +3961,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>92554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R32" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4029,12 +4037,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,71 +4058,63 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B33" t="n">
-        <v>92554</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R33" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2460,7 +2460,7 @@
         <v>128885467</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>128886816</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128885716</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128885337</v>
       </c>
       <c r="B22" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>128885509</v>
       </c>
       <c r="B23" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>128886952</v>
       </c>
       <c r="B24" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,32 +3305,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128893894</v>
+        <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,11 +3340,10 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3352,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567377</v>
+        <v>567289</v>
       </c>
       <c r="R26" t="n">
-        <v>6432177</v>
+        <v>6432071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3415,32 +3414,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128893756</v>
+        <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>92822</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3450,10 +3449,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567289</v>
+        <v>567377</v>
       </c>
       <c r="R27" t="n">
-        <v>6432071</v>
+        <v>6432177</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91959</v>
+        <v>91962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86845</v>
+        <v>86848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>128902008</v>
       </c>
       <c r="B32" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128893564</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3961,59 +3961,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128902008</v>
+        <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>92557</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 39295, Vårum, Sm</t>
+          <t>Vårum-Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567412</v>
+        <v>567533</v>
       </c>
       <c r="R32" t="n">
-        <v>6432068</v>
+        <v>6432053</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4037,12 +4029,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,63 +4050,71 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128893564</v>
+        <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>92557</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vårum-Dalhem, Sm</t>
+          <t>A 39295, Vårum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567533</v>
+        <v>567412</v>
       </c>
       <c r="R33" t="n">
-        <v>6432053</v>
+        <v>6432068</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4159,12 +4159,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -3199,7 +3199,7 @@
         <v>128901291</v>
       </c>
       <c r="B25" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>128893756</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Susanne Hernqvist, Jan Aronsson</t>
+          <t>Jan Aronsson, Susanne Hernqvist, Stefan Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
         <v>128893894</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128834653</v>
       </c>
       <c r="B28" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>128894108</v>
       </c>
       <c r="B29" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>128893759</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Jan Aronsson, Stefan Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3855,7 +3855,7 @@
         <v>128896818</v>
       </c>
       <c r="B31" t="n">
-        <v>86848</v>
+        <v>86850</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>128893564</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>128902008</v>
       </c>
       <c r="B33" t="n">
-        <v>92557</v>
+        <v>92559</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>128896704</v>
       </c>
       <c r="B34" t="n">
-        <v>86890</v>
+        <v>86892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>128901081</v>
       </c>
       <c r="B35" t="n">
-        <v>87064</v>
+        <v>87066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4376,7 +4376,7 @@
         <v>129149145</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56908</v>
+        <v>56921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -2237,7 +2237,7 @@
         <v>128834675</v>
       </c>
       <c r="B16" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4485,7 +4485,7 @@
         <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>96234</v>
+        <v>96237</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>130450141</v>
       </c>
       <c r="B38" t="n">
-        <v>96245</v>
+        <v>96248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>130450134</v>
       </c>
       <c r="B39" t="n">
-        <v>87028</v>
+        <v>87031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130450132</v>
+        <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>91712</v>
+        <v>97596</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567583</v>
+        <v>567217</v>
       </c>
       <c r="R40" t="n">
-        <v>6432052</v>
+        <v>6432025</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130450171</v>
+        <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>97593</v>
+        <v>91715</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567217</v>
+        <v>567583</v>
       </c>
       <c r="R41" t="n">
-        <v>6432025</v>
+        <v>6432052</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75270</v>
+        <v>75273</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96362</v>
+        <v>96365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92110</v>
+        <v>92113</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450169</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450260</v>
       </c>
       <c r="B48" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96039</v>
+        <v>96042</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92506</v>
+        <v>92509</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130450087</v>
+        <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>92023</v>
+        <v>97169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>567162</v>
+        <v>567383</v>
       </c>
       <c r="R52" t="n">
-        <v>6432113</v>
+        <v>6432076</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,10 +6034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130450078</v>
+        <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>97166</v>
+        <v>92026</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>567383</v>
+        <v>567162</v>
       </c>
       <c r="R53" t="n">
-        <v>6432076</v>
+        <v>6432113</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96245</v>
+        <v>96248</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>96237</v>
+        <v>87057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R37" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450141</v>
+        <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>96248</v>
+        <v>96263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567195</v>
+        <v>567155</v>
       </c>
       <c r="R38" t="n">
-        <v>6432031</v>
+        <v>6432130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130450134</v>
+        <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>87031</v>
+        <v>96274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>427</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567497</v>
+        <v>567195</v>
       </c>
       <c r="R39" t="n">
-        <v>6432034</v>
+        <v>6432031</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97596</v>
+        <v>97622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>91973</v>
+        <v>91999</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75273</v>
+        <v>75299</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96365</v>
+        <v>96391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92113</v>
+        <v>92139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>98923</v>
+        <v>93039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R47" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>93013</v>
+        <v>98949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R48" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96042</v>
+        <v>96068</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92509</v>
+        <v>92535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92026</v>
+        <v>92052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96248</v>
+        <v>96274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4485,7 +4485,7 @@
         <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>87057</v>
+        <v>87058</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>96263</v>
+        <v>96264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96274</v>
+        <v>96275</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97622</v>
+        <v>97623</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>91741</v>
+        <v>91742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>91999</v>
+        <v>92000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91741</v>
+        <v>91742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96391</v>
+        <v>96392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92139</v>
+        <v>92140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91741</v>
+        <v>91742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96068</v>
+        <v>96069</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92052</v>
+        <v>92053</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96274</v>
+        <v>96275</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>87058</v>
+        <v>96265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R37" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>96264</v>
+        <v>87059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R38" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96275</v>
+        <v>96276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130450171</v>
+        <v>130450132</v>
       </c>
       <c r="B40" t="n">
-        <v>97623</v>
+        <v>91743</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567217</v>
+        <v>567583</v>
       </c>
       <c r="R40" t="n">
-        <v>6432025</v>
+        <v>6432052</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130450132</v>
+        <v>130450171</v>
       </c>
       <c r="B41" t="n">
-        <v>91742</v>
+        <v>97624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567583</v>
+        <v>567217</v>
       </c>
       <c r="R41" t="n">
-        <v>6432052</v>
+        <v>6432025</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92000</v>
+        <v>92001</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91742</v>
+        <v>91743</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96392</v>
+        <v>96393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91742</v>
+        <v>91743</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92536</v>
+        <v>92537</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96275</v>
+        <v>96276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4485,7 +4485,7 @@
         <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>96265</v>
+        <v>96267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>87059</v>
+        <v>87061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96276</v>
+        <v>96278</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130450132</v>
+        <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>91743</v>
+        <v>97626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567583</v>
+        <v>567217</v>
       </c>
       <c r="R40" t="n">
-        <v>6432052</v>
+        <v>6432025</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130450171</v>
+        <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>97624</v>
+        <v>91745</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567217</v>
+        <v>567583</v>
       </c>
       <c r="R41" t="n">
-        <v>6432025</v>
+        <v>6432052</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92001</v>
+        <v>92003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91743</v>
+        <v>91745</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75299</v>
+        <v>75301</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96393</v>
+        <v>96395</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92141</v>
+        <v>92143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91743</v>
+        <v>91745</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96070</v>
+        <v>96072</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92537</v>
+        <v>92539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92054</v>
+        <v>92056</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96276</v>
+        <v>96278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>96267</v>
+        <v>87061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R37" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>87061</v>
+        <v>96271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R38" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96278</v>
+        <v>96282</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97626</v>
+        <v>97630</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96395</v>
+        <v>96399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96072</v>
+        <v>96076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92539</v>
+        <v>92543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96278</v>
+        <v>96282</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>87061</v>
+        <v>96271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R37" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>96271</v>
+        <v>87061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R38" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B47" t="n">
-        <v>93047</v>
+        <v>98957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R47" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B48" t="n">
-        <v>98957</v>
+        <v>93047</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R48" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>98957</v>
+        <v>93047</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R47" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>93047</v>
+        <v>98957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R48" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4485,7 +4485,7 @@
         <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>96271</v>
+        <v>96284</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>87061</v>
+        <v>87071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96282</v>
+        <v>96295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97630</v>
+        <v>97643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>91745</v>
+        <v>91758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92003</v>
+        <v>92016</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91745</v>
+        <v>91758</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75301</v>
+        <v>75309</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96399</v>
+        <v>96412</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92143</v>
+        <v>92156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B47" t="n">
-        <v>93047</v>
+        <v>98970</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R47" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B48" t="n">
-        <v>98957</v>
+        <v>93060</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R48" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91745</v>
+        <v>91758</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96076</v>
+        <v>96089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92543</v>
+        <v>92556</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92056</v>
+        <v>92069</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96282</v>
+        <v>96295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>96284</v>
+        <v>87072</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R37" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>87071</v>
+        <v>96285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R38" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97643</v>
+        <v>97644</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75309</v>
+        <v>75310</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96412</v>
+        <v>96413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92156</v>
+        <v>92157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>98970</v>
+        <v>93061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R47" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>93060</v>
+        <v>98971</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R48" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96089</v>
+        <v>96090</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92556</v>
+        <v>92557</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>87072</v>
+        <v>96288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R37" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>96285</v>
+        <v>87073</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R38" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96296</v>
+        <v>96299</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130450171</v>
+        <v>130450132</v>
       </c>
       <c r="B40" t="n">
-        <v>97644</v>
+        <v>91760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567217</v>
+        <v>567583</v>
       </c>
       <c r="R40" t="n">
-        <v>6432025</v>
+        <v>6432052</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130450132</v>
+        <v>130450171</v>
       </c>
       <c r="B41" t="n">
-        <v>91759</v>
+        <v>97647</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567583</v>
+        <v>567217</v>
       </c>
       <c r="R41" t="n">
-        <v>6432052</v>
+        <v>6432025</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92017</v>
+        <v>92018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91759</v>
+        <v>91760</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>130450126</v>
       </c>
       <c r="B44" t="n">
-        <v>75310</v>
+        <v>75311</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96413</v>
+        <v>96416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92157</v>
+        <v>92158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91759</v>
+        <v>91760</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96090</v>
+        <v>96093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92557</v>
+        <v>92558</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96296</v>
+        <v>96299</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4773,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130450132</v>
+        <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>91760</v>
+        <v>97647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567583</v>
+        <v>567217</v>
       </c>
       <c r="R40" t="n">
-        <v>6432052</v>
+        <v>6432025</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130450171</v>
+        <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>97647</v>
+        <v>91760</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567217</v>
+        <v>567583</v>
       </c>
       <c r="R41" t="n">
-        <v>6432025</v>
+        <v>6432052</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5258,32 +5258,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130450219</v>
+        <v>130450153</v>
       </c>
       <c r="B45" t="n">
-        <v>96416</v>
+        <v>92158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>1506</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>567485</v>
+        <v>567410</v>
       </c>
       <c r="R45" t="n">
-        <v>6432073</v>
+        <v>6432143</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,32 +5355,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130450153</v>
+        <v>130450219</v>
       </c>
       <c r="B46" t="n">
-        <v>92158</v>
+        <v>96416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>567410</v>
+        <v>567485</v>
       </c>
       <c r="R46" t="n">
-        <v>6432143</v>
+        <v>6432073</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130450078</v>
+        <v>130450087</v>
       </c>
       <c r="B52" t="n">
-        <v>97220</v>
+        <v>92071</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>567383</v>
+        <v>567162</v>
       </c>
       <c r="R52" t="n">
-        <v>6432076</v>
+        <v>6432113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,10 +6034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130450087</v>
+        <v>130450078</v>
       </c>
       <c r="B53" t="n">
-        <v>92071</v>
+        <v>97220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>567162</v>
+        <v>567383</v>
       </c>
       <c r="R53" t="n">
-        <v>6432113</v>
+        <v>6432076</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>96288</v>
+        <v>87073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R37" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>87073</v>
+        <v>96288</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R38" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5258,32 +5258,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130450153</v>
+        <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>92158</v>
+        <v>96416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1506</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>567410</v>
+        <v>567485</v>
       </c>
       <c r="R45" t="n">
-        <v>6432143</v>
+        <v>6432073</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,32 +5355,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130450219</v>
+        <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>96416</v>
+        <v>92158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>567485</v>
+        <v>567410</v>
       </c>
       <c r="R46" t="n">
-        <v>6432073</v>
+        <v>6432143</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130450087</v>
+        <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>92071</v>
+        <v>97220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>567162</v>
+        <v>567383</v>
       </c>
       <c r="R52" t="n">
-        <v>6432113</v>
+        <v>6432076</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,10 +6034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130450078</v>
+        <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>97220</v>
+        <v>92071</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>567383</v>
+        <v>567162</v>
       </c>
       <c r="R53" t="n">
-        <v>6432076</v>
+        <v>6432113</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>87073</v>
+        <v>96288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R37" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>96288</v>
+        <v>87073</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R38" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B47" t="n">
-        <v>93062</v>
+        <v>98974</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R47" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B48" t="n">
-        <v>98974</v>
+        <v>93062</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R48" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B37" t="n">
-        <v>96288</v>
+        <v>87073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R37" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B38" t="n">
-        <v>87073</v>
+        <v>96297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R38" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>130450141</v>
       </c>
       <c r="B39" t="n">
-        <v>96299</v>
+        <v>96308</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>130450171</v>
       </c>
       <c r="B40" t="n">
-        <v>97647</v>
+        <v>97656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>130450132</v>
       </c>
       <c r="B41" t="n">
-        <v>91760</v>
+        <v>91768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>130450157</v>
       </c>
       <c r="B42" t="n">
-        <v>92018</v>
+        <v>92026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>130450131</v>
       </c>
       <c r="B43" t="n">
-        <v>91760</v>
+        <v>91768</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>130450219</v>
       </c>
       <c r="B45" t="n">
-        <v>96416</v>
+        <v>96425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>130450153</v>
       </c>
       <c r="B46" t="n">
-        <v>92158</v>
+        <v>92166</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130450169</v>
+        <v>130450260</v>
       </c>
       <c r="B47" t="n">
-        <v>98974</v>
+        <v>93071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567453</v>
+        <v>567479</v>
       </c>
       <c r="R47" t="n">
-        <v>6432049</v>
+        <v>6432123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,32 +5549,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130450260</v>
+        <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>93062</v>
+        <v>98988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>567479</v>
+        <v>567453</v>
       </c>
       <c r="R48" t="n">
-        <v>6432123</v>
+        <v>6432049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5649,7 +5649,7 @@
         <v>130450133</v>
       </c>
       <c r="B49" t="n">
-        <v>91760</v>
+        <v>91768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>130450201</v>
       </c>
       <c r="B50" t="n">
-        <v>96093</v>
+        <v>96102</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>130450158</v>
       </c>
       <c r="B51" t="n">
-        <v>92558</v>
+        <v>92566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130450078</v>
       </c>
       <c r="B52" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>130450087</v>
       </c>
       <c r="B53" t="n">
-        <v>92071</v>
+        <v>92079</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130450137</v>
       </c>
       <c r="B54" t="n">
-        <v>96299</v>
+        <v>96308</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 39295-2024 artfynd.xlsx
+++ b/artfynd/A 39295-2024 artfynd.xlsx
@@ -4482,32 +4482,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130450134</v>
+        <v>130450239</v>
       </c>
       <c r="B37" t="n">
-        <v>87073</v>
+        <v>96297</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567497</v>
+        <v>567155</v>
       </c>
       <c r="R37" t="n">
-        <v>6432034</v>
+        <v>6432130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130450239</v>
+        <v>130450134</v>
       </c>
       <c r="B38" t="n">
-        <v>96297</v>
+        <v>87073</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>427</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567155</v>
+        <v>567497</v>
       </c>
       <c r="R38" t="n">
-        <v>6432130</v>
+        <v>6432034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5552,7 +5552,7 @@
         <v>130450169</v>
       </c>
       <c r="B48" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
